--- a/plantilla_incoming_calidad.xlsx
+++ b/plantilla_incoming_calidad.xlsx
@@ -454,20 +454,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="42" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -483,45 +484,50 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Placa</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Galvanizado_o_Decapado</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Espesor_Medido_1_in</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Espesor_Medido_2_in</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Espesor_Medido_3_in</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Cantidad_Hojas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Peso_Total_Kg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Num_Colada</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Lote_Heat</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -538,37 +544,40 @@
           <t>CAL 14</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Galvanizado</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="E2" s="2" t="n">
         <v>0.07480000000000001</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>0.0752</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.075</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>2500</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>COL-982145</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>LOT-9921</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Excelente estado superficial</t>
         </is>
@@ -585,37 +594,40 @@
           <t>CAL 12</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Decapado</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="E3" s="2" t="n">
         <v>0.1042</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="F3" s="2" t="n">
         <v>0.1048</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.1045</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>120</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>3200</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>COL-772151</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>LOT-8812</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Liberado condicionado por óxido ligero</t>
         </is>
@@ -626,7 +638,7 @@
     <dataValidation sqref="B2:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Calibre Inválido" error="El calibre ingresado debe pertenecer a la lista del catálogo (CAL 10, CAL 12, CAL 14, CAL 16)." promptTitle="Calibre" prompt="Seleccione el calibre del catálogo" type="list">
       <formula1>"CAL 10,CAL 12,CAL 14,CAL 16"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Material Inválido" error="El tipo de material debe ser Galvanizado, Decapado o Aluminio." promptTitle="Material" prompt="Seleccione el tipo de material" type="list">
+    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Material Inválido" error="El tipo de material debe ser Galvanizado, Decapado o Aluminio." promptTitle="Material" prompt="Seleccione el tipo de material" type="list">
       <formula1>"Galvanizado,Decapado,Aluminio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/plantilla_incoming_calidad.xlsx
+++ b/plantilla_incoming_calidad.xlsx
@@ -454,191 +454,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>HOJA 1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>HOJA 2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>HOJA 3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>HOJA 4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>No_Atado</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Calibre</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Placa</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>Galvanizado_o_Decapado</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Espesor_Medido_1_in</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Espesor_Medido_2_in</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Espesor_Medido_3_in</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_1</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_2</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_3</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_4</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_5</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_6</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_7</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_8</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_9</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_4</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_5</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>Espesor_6</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Cantidad_Hojas</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Peso_Total_Kg</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Num_Colada</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Lote_Heat</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Observaciones</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>AT-TERNIUM-4521</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>CAL 14</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Galvanizado</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>0.07480000000000001</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.0752</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>150</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>COL-982145</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>LOT-9921</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>Excelente estado superficial</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AT-NUCOR-9912</t>
+          <t>ACEROMEX 01</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>CAL 12</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+          <t>CAL 16</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Decapado</t>
         </is>
       </c>
+      <c r="D3" s="2" t="n">
+        <v>0.059</v>
+      </c>
       <c r="E3" s="2" t="n">
-        <v>0.1042</v>
+        <v>0.059</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.1048</v>
+        <v>0.06</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.1045</v>
+        <v>0.059</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>120</v>
+        <v>0.059</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>COL-772151</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>LOT-8812</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>Liberado condicionado por óxido ligero</t>
+        <v>0.059</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>COL-2603210220</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>LOT-23587</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Material con daños en el acabado (óxido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ACEROMEX 02</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CAL 16</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Decapado</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>2029</v>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>COL-2603210220</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>LOT-23587</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>Excelente estado superficial</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:I1"/>
+    <mergeCell ref="M1:O1"/>
+  </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Calibre Inválido" error="El calibre ingresado debe pertenecer a la lista del catálogo (CAL 10, CAL 12, CAL 14, CAL 16)." promptTitle="Calibre" prompt="Seleccione el calibre del catálogo" type="list">
+    <dataValidation sqref="B3:B100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Calibre Inválido" error="El calibre ingresado debe pertenecer a la lista del catálogo (CAL 10, CAL 12, CAL 14, CAL 16)." promptTitle="Calibre" prompt="Seleccione el calibre del catálogo" type="list">
       <formula1>"CAL 10,CAL 12,CAL 14,CAL 16"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Material Inválido" error="El tipo de material debe ser Galvanizado, Decapado o Aluminio." promptTitle="Material" prompt="Seleccione el tipo de material" type="list">
+    <dataValidation sqref="C3:C100" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Material Inválido" error="El tipo de material debe ser Galvanizado, Decapado o Aluminio." promptTitle="Material" prompt="Seleccione el tipo de material" type="list">
       <formula1>"Galvanizado,Decapado,Aluminio"</formula1>
     </dataValidation>
   </dataValidations>

--- a/plantilla_incoming_calidad.xlsx
+++ b/plantilla_incoming_calidad.xlsx
@@ -460,18 +460,18 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="8.5" customWidth="1" min="4" max="4"/>
+    <col width="8.5" customWidth="1" min="5" max="5"/>
+    <col width="8.5" customWidth="1" min="6" max="6"/>
+    <col width="8.5" customWidth="1" min="7" max="7"/>
+    <col width="8.5" customWidth="1" min="8" max="8"/>
+    <col width="8.5" customWidth="1" min="9" max="9"/>
+    <col width="8.5" customWidth="1" min="10" max="10"/>
+    <col width="8.5" customWidth="1" min="11" max="11"/>
+    <col width="8.5" customWidth="1" min="12" max="12"/>
+    <col width="8.5" customWidth="1" min="13" max="13"/>
+    <col width="8.5" customWidth="1" min="14" max="14"/>
+    <col width="8.5" customWidth="1" min="15" max="15"/>
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="18" customWidth="1" min="18" max="18"/>

--- a/plantilla_incoming_calidad.xlsx
+++ b/plantilla_incoming_calidad.xlsx
@@ -457,9 +457,9 @@
   <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="8.5" customWidth="1" min="4" max="4"/>
     <col width="8.5" customWidth="1" min="5" max="5"/>
     <col width="8.5" customWidth="1" min="6" max="6"/>
